--- a/tools/importer/reports/import-content-landing.report.xlsx
+++ b/tools/importer/reports/import-content-landing.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="50">
   <si>
     <t>_reportFile</t>
   </si>
@@ -37,6 +37,30 @@
     <t>url</t>
   </si>
   <si>
+    <t>blog.report.json</t>
+  </si>
+  <si>
+    <t>["columns-intro","columns-article","cards-article"]</t>
+  </si>
+  <si>
+    <t>blog</t>
+  </si>
+  <si>
+    <t>success</t>
+  </si>
+  <si>
+    <t>listing-index</t>
+  </si>
+  <si>
+    <t>2026-08-30T17:00:25.063Z</t>
+  </si>
+  <si>
+    <t>Blog — WKND Trendsetters</t>
+  </si>
+  <si>
+    <t>https://www.wknd-trendsetters.site/blog</t>
+  </si>
+  <si>
     <t>faq.report.json</t>
   </si>
   <si>
@@ -46,9 +70,6 @@
     <t>faq</t>
   </si>
   <si>
-    <t>success</t>
-  </si>
-  <si>
     <t>faq-page</t>
   </si>
   <si>
@@ -61,6 +82,27 @@
     <t>https://www.wknd-trendsetters.site/faq</t>
   </si>
   <si>
+    <t>fashion-trends-of-the-season.report.json</t>
+  </si>
+  <si>
+    <t>["columns-intro","columns-article"]</t>
+  </si>
+  <si>
+    <t>fashion-trends-of-the-season</t>
+  </si>
+  <si>
+    <t>content-landing</t>
+  </si>
+  <si>
+    <t>2026-08-31T04:52:48.147Z</t>
+  </si>
+  <si>
+    <t>Top Fashion Trends for Young People | Fashion Blog</t>
+  </si>
+  <si>
+    <t>https://www.wknd-trendsetters.site/fashion-trends-of-the-season</t>
+  </si>
+  <si>
     <t>fashion-trends-young-adults-casual-sport.report.json</t>
   </si>
   <si>
@@ -73,7 +115,7 @@
     <t>cards-showcase</t>
   </si>
   <si>
-    <t>2026-08-30T16:59:51.294Z</t>
+    <t>2026-08-30T19:03:54.003Z</t>
   </si>
   <si>
     <t>Fashion Trends for Young Adults | Fashion Blog</t>
@@ -89,9 +131,6 @@
   </si>
   <si>
     <t>index</t>
-  </si>
-  <si>
-    <t>content-landing</t>
   </si>
   <si>
     <t>2026-08-30T17:00:20.576Z</t>
@@ -510,7 +549,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="50" customWidth="1"/>
@@ -650,6 +689,58 @@
         <v>36</v>
       </c>
     </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
+      </c>
+      <c r="G7" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" t="s">
+        <v>49</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
